--- a/SGC-CKN/Excel/c93f9825-0201-4d0b-83d8-bb39854a5cce_Lô_CT-02_P7-29_D800_07-03-2026.xlsx
+++ b/SGC-CKN/Excel/c93f9825-0201-4d0b-83d8-bb39854a5cce_Lô_CT-02_P7-29_D800_07-03-2026.xlsx
@@ -1226,7 +1226,7 @@
         <v>0.28</v>
       </c>
       <c r="I11" s="5">
-        <v>6.5</v>
+        <v>2.69</v>
       </c>
       <c r="J11" s="8">
         <v>9.49</v>
@@ -1673,10 +1673,10 @@
         <v>0.28</v>
       </c>
       <c r="H2" s="5">
-        <v>6.5</v>
+        <v>2.69</v>
       </c>
       <c r="I2" s="8">
-        <v>22.94</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1934,10 +1934,10 @@
         <v>29.12</v>
       </c>
       <c r="H11" s="37">
-        <v>45.18</v>
+        <v>41.37</v>
       </c>
       <c r="I11" s="37">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/c93f9825-0201-4d0b-83d8-bb39854a5cce_Lô_CT-02_P7-29_D800_07-03-2026.xlsx
+++ b/SGC-CKN/Excel/c93f9825-0201-4d0b-83d8-bb39854a5cce_Lô_CT-02_P7-29_D800_07-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -112,7 +112,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">09:18
@@ -140,7 +140,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">05:05
@@ -154,7 +154,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">05:43
@@ -168,7 +168,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:15
@@ -182,7 +182,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:30
@@ -193,10 +193,10 @@
 07/03/2026</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>TK-16.1</t>
+  </si>
+  <si>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:18
@@ -205,9 +205,6 @@
   <si>
     <t xml:space="preserve">11:15
 07/03/2026</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:16
@@ -1488,13 +1485,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="E19" s="34" t="s">
         <v>60</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>61</v>
       </c>
       <c r="F19" s="32">
         <v>-39.65</v>
@@ -1517,7 +1514,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
@@ -1623,31 +1620,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1890,7 +1887,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1913,7 +1910,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="37" t="s">
         <v>30</v>
